--- a/data/extra_material/raw_task_load_index.xlsx
+++ b/data/extra_material/raw_task_load_index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\Chatbot-Evaluation-Framework\data\extra_material\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\CEP-guide\data\extra_material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D03B6FF-C5A0-4266-8C39-56691195ACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE21E0E-2213-4AFF-9C7D-C036C2033D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>Subscale</t>
   </si>
@@ -97,6 +97,12 @@
   </si>
   <si>
     <t>rtlx6</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>0 to 100 in 5 point steps (0 - low; 100 - high)</t>
   </si>
 </sst>
 </file>
@@ -429,16 +435,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -451,8 +458,11 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -465,8 +475,11 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -479,8 +492,11 @@
       <c r="D3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -493,8 +509,11 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -507,8 +526,11 @@
       <c r="D5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -521,8 +543,11 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -534,6 +559,9 @@
       </c>
       <c r="D7" t="s">
         <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
